--- a/data/final/validity_results_all.xlsx
+++ b/data/final/validity_results_all.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -427,6 +427,16 @@
           <t>LoA_upper</t>
         </is>
       </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>BA_slope</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>BA_slope_p</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -473,6 +483,12 @@
       <c r="N2">
         <v>87.13213895518319</v>
       </c>
+      <c r="O2">
+        <v>0.2540754335369597</v>
+      </c>
+      <c r="P2">
+        <v>1.478740053326337E-10</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -518,6 +534,12 @@
       </c>
       <c r="N3">
         <v>-6.483318197415642</v>
+      </c>
+      <c r="O3">
+        <v>-0.6626040291396081</v>
+      </c>
+      <c r="P3">
+        <v>6.40312732578966E-31</v>
       </c>
     </row>
   </sheetData>
@@ -527,7 +549,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -601,6 +623,16 @@
           <t>LoA_upper</t>
         </is>
       </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>BA_slope</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>BA_slope_p</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -647,6 +679,12 @@
       <c r="N2">
         <v>1724.868786502032</v>
       </c>
+      <c r="O2">
+        <v>1.097961214607456</v>
+      </c>
+      <c r="P2">
+        <v>1.02515645142164E-27</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -693,6 +731,12 @@
       <c r="N3">
         <v>1299.876214717267</v>
       </c>
+      <c r="O3">
+        <v>0.5671736437324914</v>
+      </c>
+      <c r="P3">
+        <v>4.021153234102253E-14</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -738,6 +782,12 @@
       </c>
       <c r="N4">
         <v>1548.031194279133</v>
+      </c>
+      <c r="O4">
+        <v>0.7692751327749411</v>
+      </c>
+      <c r="P4">
+        <v>3.572251522094927E-16</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/validity_results_all.xlsx
+++ b/data/final/validity_results_all.xlsx
@@ -448,46 +448,46 @@
         <v>120</v>
       </c>
       <c r="C2">
-        <v>0.9234101115287354</v>
+        <v>0.9234101115287343</v>
       </c>
       <c r="D2">
-        <v>0.8917682464640166</v>
+        <v>0.8917682464640151</v>
       </c>
       <c r="E2">
-        <v>0.9460651232431769</v>
+        <v>0.9460651232431762</v>
       </c>
       <c r="F2">
-        <v>6.689872626229933E-51</v>
+        <v>6.689872626235456E-51</v>
       </c>
       <c r="G2">
-        <v>0.8526862340735116</v>
+        <v>0.8526862340735095</v>
       </c>
       <c r="H2">
-        <v>0.8421603242505259</v>
+        <v>0.8421594323834386</v>
       </c>
       <c r="I2">
-        <v>0.5202858641317637</v>
+        <v>0.5202782558418642</v>
       </c>
       <c r="J2">
-        <v>0.9288352378944715</v>
+        <v>0.9288352161356226</v>
       </c>
       <c r="K2">
-        <v>40.28367145604221</v>
+        <v>40.2836714560441</v>
       </c>
       <c r="L2">
-        <v>25.06961702256125</v>
+        <v>25.06961702256327</v>
       </c>
       <c r="M2">
-        <v>-36.99290491006071</v>
+        <v>-36.99290491006023</v>
       </c>
       <c r="N2">
-        <v>87.13213895518319</v>
+        <v>87.13213895518678</v>
       </c>
       <c r="O2">
-        <v>0.2540754335369597</v>
+        <v>0.2540754335369901</v>
       </c>
       <c r="P2">
-        <v>1.478740053326337E-10</v>
+        <v>1.478740053320287E-10</v>
       </c>
     </row>
     <row r="3">
@@ -500,46 +500,46 @@
         <v>120</v>
       </c>
       <c r="C3">
-        <v>0.8788008425067078</v>
+        <v>0.8257433869993704</v>
       </c>
       <c r="D3">
-        <v>0.8303548779173361</v>
+        <v>0.7588117670250647</v>
       </c>
       <c r="E3">
-        <v>0.9140615469034061</v>
+        <v>0.8754166301377868</v>
       </c>
       <c r="F3">
-        <v>1.01290386508408E-39</v>
+        <v>3.996430560945545E-31</v>
       </c>
       <c r="G3">
-        <v>0.7722909207904993</v>
+        <v>0.681852141173192</v>
       </c>
       <c r="H3">
-        <v>0.2598665410598678</v>
+        <v>0.8221427192577244</v>
       </c>
       <c r="I3">
-        <v>-0.06242129397358923</v>
+        <v>0.7541126707309673</v>
       </c>
       <c r="J3">
-        <v>0.6097641350755771</v>
+        <v>0.872684309057678</v>
       </c>
       <c r="K3">
-        <v>30.92786156283232</v>
+        <v>5.814805148316804</v>
       </c>
       <c r="L3">
-        <v>-28.77873304890491</v>
+        <v>-0.9106382282781132</v>
       </c>
       <c r="M3">
-        <v>-51.07414790039419</v>
+        <v>-12.21422560529622</v>
       </c>
       <c r="N3">
-        <v>-6.483318197415642</v>
+        <v>10.39294914874</v>
       </c>
       <c r="O3">
-        <v>-0.6626040291396081</v>
+        <v>0.05921723355329524</v>
       </c>
       <c r="P3">
-        <v>6.40312732578966E-31</v>
+        <v>0.2995813249308721</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/validity_results_all.xlsx
+++ b/data/final/validity_results_all.xlsx
@@ -448,46 +448,46 @@
         <v>120</v>
       </c>
       <c r="C2">
-        <v>0.9234101115287343</v>
+        <v>0.9285464656680077</v>
       </c>
       <c r="D2">
-        <v>0.8917682464640151</v>
+        <v>0.8989150797862341</v>
       </c>
       <c r="E2">
-        <v>0.9460651232431762</v>
+        <v>0.9497218774612791</v>
       </c>
       <c r="F2">
-        <v>6.689872626235456E-51</v>
+        <v>1.296206754724083E-52</v>
       </c>
       <c r="G2">
-        <v>0.8526862340735095</v>
+        <v>0.8621985389045486</v>
       </c>
       <c r="H2">
-        <v>0.8421594323834386</v>
+        <v>0.8591654466346518</v>
       </c>
       <c r="I2">
-        <v>0.5202782558418642</v>
+        <v>0.5545109490961133</v>
       </c>
       <c r="J2">
-        <v>0.9288352161356226</v>
+        <v>0.9373308991186499</v>
       </c>
       <c r="K2">
-        <v>40.2836714560441</v>
+        <v>38.43649968560339</v>
       </c>
       <c r="L2">
-        <v>25.06961702256327</v>
+        <v>23.96261885742639</v>
       </c>
       <c r="M2">
-        <v>-36.99290491006023</v>
+        <v>-35.18740680094105</v>
       </c>
       <c r="N2">
-        <v>87.13213895518678</v>
+        <v>83.11264451579383</v>
       </c>
       <c r="O2">
-        <v>0.2540754335369901</v>
+        <v>0.21808627111409</v>
       </c>
       <c r="P2">
-        <v>1.478740053320287E-10</v>
+        <v>7.610740390706425E-09</v>
       </c>
     </row>
     <row r="3">
@@ -500,46 +500,46 @@
         <v>120</v>
       </c>
       <c r="C3">
-        <v>0.8257433869993704</v>
+        <v>0.8940685828270424</v>
       </c>
       <c r="D3">
-        <v>0.7588117670250647</v>
+        <v>0.8512422641150903</v>
       </c>
       <c r="E3">
-        <v>0.8754166301377868</v>
+        <v>0.9250645769289254</v>
       </c>
       <c r="F3">
-        <v>3.996430560945545E-31</v>
+        <v>5.696561730512083E-43</v>
       </c>
       <c r="G3">
-        <v>0.681852141173192</v>
+        <v>0.7993586307983559</v>
       </c>
       <c r="H3">
-        <v>0.8221427192577244</v>
+        <v>0.885204988757987</v>
       </c>
       <c r="I3">
-        <v>0.7541126707309673</v>
+        <v>0.8327153777491232</v>
       </c>
       <c r="J3">
-        <v>0.872684309057678</v>
+        <v>0.9208757087628935</v>
       </c>
       <c r="K3">
-        <v>5.814805148316804</v>
+        <v>4.650728550785716</v>
       </c>
       <c r="L3">
-        <v>-0.9106382282781132</v>
+        <v>-1.263766292333848</v>
       </c>
       <c r="M3">
-        <v>-12.21422560529622</v>
+        <v>-10.07298152398733</v>
       </c>
       <c r="N3">
-        <v>10.39294914874</v>
+        <v>7.54544893931963</v>
       </c>
       <c r="O3">
-        <v>0.05921723355329524</v>
+        <v>0.07240836398804608</v>
       </c>
       <c r="P3">
-        <v>0.2995813249308721</v>
+        <v>0.0985577792911069</v>
       </c>
     </row>
   </sheetData>
@@ -644,46 +644,46 @@
         <v>120</v>
       </c>
       <c r="C2">
-        <v>0.5361693706521965</v>
+        <v>0.5385840956096606</v>
       </c>
       <c r="D2">
-        <v>0.39487719761245</v>
+        <v>0.3977391120410336</v>
       </c>
       <c r="E2">
-        <v>0.6526852334416594</v>
+        <v>0.6546297474855457</v>
       </c>
       <c r="F2">
-        <v>2.769074555762064E-10</v>
+        <v>2.223243061557584E-10</v>
       </c>
       <c r="G2">
-        <v>0.2874775940255725</v>
+        <v>0.290072828043676</v>
       </c>
       <c r="H2">
-        <v>0.1267389797626698</v>
+        <v>0.1425598127690257</v>
       </c>
       <c r="I2">
-        <v>-0.07532847367872272</v>
+        <v>-0.07929711347188015</v>
       </c>
       <c r="J2">
-        <v>0.3538929188651397</v>
+        <v>0.3821504563039979</v>
       </c>
       <c r="K2">
-        <v>926.3516380285677</v>
+        <v>895.1988232102178</v>
       </c>
       <c r="L2">
-        <v>797.6059448926103</v>
+        <v>762.9841460727399</v>
       </c>
       <c r="M2">
-        <v>-129.6568967168112</v>
+        <v>-158.5878583432446</v>
       </c>
       <c r="N2">
-        <v>1724.868786502032</v>
+        <v>1684.556150488725</v>
       </c>
       <c r="O2">
-        <v>1.097961214607456</v>
+        <v>1.040481217988644</v>
       </c>
       <c r="P2">
-        <v>1.02515645142164E-27</v>
+        <v>4.949763475210182E-25</v>
       </c>
     </row>
     <row r="3">
@@ -696,46 +696,46 @@
         <v>120</v>
       </c>
       <c r="C3">
-        <v>0.7411690711393538</v>
+        <v>0.7371366655926104</v>
       </c>
       <c r="D3">
-        <v>0.6480153660532749</v>
+        <v>0.6428293934898485</v>
       </c>
       <c r="E3">
-        <v>0.8124746648069849</v>
+        <v>0.8094315652680062</v>
       </c>
       <c r="F3">
-        <v>3.713731854592985E-22</v>
+        <v>8.10617680991494E-22</v>
       </c>
       <c r="G3">
-        <v>0.5493315920135725</v>
+        <v>0.5433704637609919</v>
       </c>
       <c r="H3">
-        <v>0.373646364994715</v>
+        <v>0.3966429656571213</v>
       </c>
       <c r="I3">
-        <v>-0.09897020973659978</v>
+        <v>-0.09376401631060158</v>
       </c>
       <c r="J3">
-        <v>0.6848268063692884</v>
+        <v>0.697212717192815</v>
       </c>
       <c r="K3">
-        <v>673.8083270527195</v>
+        <v>643.2109732481516</v>
       </c>
       <c r="L3">
-        <v>558.788924311665</v>
+        <v>520.5266029602194</v>
       </c>
       <c r="M3">
-        <v>-182.2983660939373</v>
+        <v>-223.1692530450332</v>
       </c>
       <c r="N3">
-        <v>1299.876214717267</v>
+        <v>1264.222458965472</v>
       </c>
       <c r="O3">
-        <v>0.5671736437324914</v>
+        <v>0.5583899820914174</v>
       </c>
       <c r="P3">
-        <v>4.021153234102253E-14</v>
+        <v>1.36675186533525E-13</v>
       </c>
     </row>
     <row r="4">
@@ -748,46 +748,46 @@
         <v>120</v>
       </c>
       <c r="C4">
-        <v>0.5975482462959646</v>
+        <v>0.6094161004081107</v>
       </c>
       <c r="D4">
-        <v>0.4684840548637</v>
+        <v>0.4829260040189801</v>
       </c>
       <c r="E4">
-        <v>0.7016401708285575</v>
+        <v>0.7109937712131081</v>
       </c>
       <c r="F4">
-        <v>5.811844977301887E-13</v>
+        <v>1.509440888614055E-13</v>
       </c>
       <c r="G4">
-        <v>0.3570639066513828</v>
+        <v>0.3713879834366284</v>
       </c>
       <c r="H4">
-        <v>0.2242670133047737</v>
+        <v>0.2435586562848266</v>
       </c>
       <c r="I4">
-        <v>-0.09257591811443243</v>
+        <v>-0.09367907203628241</v>
       </c>
       <c r="J4">
-        <v>0.5135197070161731</v>
+        <v>0.5352590155023544</v>
       </c>
       <c r="K4">
-        <v>809.1453575365662</v>
+        <v>776.7505096122189</v>
       </c>
       <c r="L4">
-        <v>677.5948546866985</v>
+        <v>641.6078778592098</v>
       </c>
       <c r="M4">
-        <v>-192.8414849057364</v>
+        <v>-220.1046171162236</v>
       </c>
       <c r="N4">
-        <v>1548.031194279133</v>
+        <v>1503.320372834643</v>
       </c>
       <c r="O4">
-        <v>0.7692751327749411</v>
+        <v>0.7576899619132227</v>
       </c>
       <c r="P4">
-        <v>3.572251522094927E-16</v>
+        <v>3.536729756249959E-16</v>
       </c>
     </row>
   </sheetData>
@@ -862,28 +862,28 @@
         <v>120</v>
       </c>
       <c r="C2">
-        <v>0.1538498597087588</v>
+        <v>0.6610114287165626</v>
       </c>
       <c r="D2">
-        <v>0.2473536435069738</v>
+        <v>0.3137309598237173</v>
       </c>
       <c r="E2">
-        <v>40.63942550267787</v>
+        <v>30.41781507850061</v>
       </c>
       <c r="F2">
-        <v>17.80173139354331</v>
+        <v>16.91250523511112</v>
       </c>
       <c r="G2">
-        <v>0.1704926299528643</v>
+        <v>0.6884104964641545</v>
       </c>
       <c r="H2">
-        <v>0.2627243618359543</v>
+        <v>0.3096164958192597</v>
       </c>
       <c r="I2">
-        <v>45.14705384557796</v>
+        <v>37.24039585310999</v>
       </c>
       <c r="J2">
-        <v>18.54236640588431</v>
+        <v>19.04679805235265</v>
       </c>
     </row>
     <row r="3">
@@ -896,28 +896,28 @@
         <v>120</v>
       </c>
       <c r="C3">
-        <v>0.1509865871483657</v>
+        <v>0.6785363375710531</v>
       </c>
       <c r="D3">
-        <v>0.2552277053229691</v>
+        <v>0.3372523805354467</v>
       </c>
       <c r="E3">
-        <v>48.8394732670852</v>
+        <v>36.90406289303272</v>
       </c>
       <c r="F3">
-        <v>21.79801137647094</v>
+        <v>21.82297916845243</v>
       </c>
       <c r="G3">
-        <v>0.1704926299528643</v>
+        <v>0.6884104964641545</v>
       </c>
       <c r="H3">
-        <v>0.2627243618359543</v>
+        <v>0.3096164958192597</v>
       </c>
       <c r="I3">
-        <v>45.14705384557796</v>
+        <v>37.24039585310999</v>
       </c>
       <c r="J3">
-        <v>18.54236640588431</v>
+        <v>19.04679805235265</v>
       </c>
     </row>
     <row r="4">
@@ -930,28 +930,28 @@
         <v>120</v>
       </c>
       <c r="C4">
-        <v>0.06791495577125557</v>
+        <v>0.1187706503569854</v>
       </c>
       <c r="D4">
-        <v>0.2492615920929209</v>
+        <v>0.3915910931802877</v>
       </c>
       <c r="E4">
-        <v>72.05605778101362</v>
+        <v>71.77890836833802</v>
       </c>
       <c r="F4">
-        <v>27.05432597260863</v>
+        <v>27.93864672198165</v>
       </c>
       <c r="G4">
-        <v>0.1704926299528643</v>
+        <v>0.6884104964641545</v>
       </c>
       <c r="H4">
-        <v>0.2627243618359543</v>
+        <v>0.3096164958192597</v>
       </c>
       <c r="I4">
-        <v>45.14705384557796</v>
+        <v>37.24039585310999</v>
       </c>
       <c r="J4">
-        <v>18.54236640588431</v>
+        <v>19.04679805235265</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/validity_results_all.xlsx
+++ b/data/final/validity_results_all.xlsx
@@ -862,7 +862,7 @@
         <v>120</v>
       </c>
       <c r="C2">
-        <v>0.6610114287165626</v>
+        <v>0.7674877758252703</v>
       </c>
       <c r="D2">
         <v>0.3137309598237173</v>
@@ -874,7 +874,7 @@
         <v>16.91250523511112</v>
       </c>
       <c r="G2">
-        <v>0.6884104964641545</v>
+        <v>0.8083568000255449</v>
       </c>
       <c r="H2">
         <v>0.3096164958192597</v>
@@ -896,7 +896,7 @@
         <v>120</v>
       </c>
       <c r="C3">
-        <v>0.6785363375710531</v>
+        <v>0.8038957420778015</v>
       </c>
       <c r="D3">
         <v>0.3372523805354467</v>
@@ -908,7 +908,7 @@
         <v>21.82297916845243</v>
       </c>
       <c r="G3">
-        <v>0.6884104964641545</v>
+        <v>0.8083568000255449</v>
       </c>
       <c r="H3">
         <v>0.3096164958192597</v>
@@ -930,7 +930,7 @@
         <v>120</v>
       </c>
       <c r="C4">
-        <v>0.1187706503569854</v>
+        <v>0.1420663889443681</v>
       </c>
       <c r="D4">
         <v>0.3915910931802877</v>
@@ -942,7 +942,7 @@
         <v>27.93864672198165</v>
       </c>
       <c r="G4">
-        <v>0.6884104964641545</v>
+        <v>0.8083568000255449</v>
       </c>
       <c r="H4">
         <v>0.3096164958192597</v>
